--- a/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
   <si>
     <t>KORE</t>
   </si>
@@ -656,129 +656,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>72500</v>
+      </c>
+      <c r="F8" s="3">
         <v>68600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>69500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>66000</v>
       </c>
-      <c r="G8" s="3">
-        <v>62500</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
+        <v>62400</v>
+      </c>
+      <c r="J8" s="3">
         <v>66100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>70900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>69000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>64300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>67900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>116000</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -791,47 +798,53 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>35500</v>
+      </c>
+      <c r="F9" s="3">
         <v>31000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>31700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>30300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>28700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>31500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>33600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>35300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>33500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>35000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>53700</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,47 +857,53 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F10" s="3">
         <v>37600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>37800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>35700</v>
       </c>
-      <c r="G10" s="3">
-        <v>33800</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>33700</v>
+      </c>
+      <c r="J10" s="3">
         <v>34600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>37300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>33700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>30800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>32900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>62300</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -897,8 +916,14 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,8 +943,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -971,8 +998,14 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,38 +1057,44 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F14" s="3">
         <v>78300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>58100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>1400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1065,11 +1104,11 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1077,47 +1116,53 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E15" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F15" s="3">
         <v>14500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>14500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>14100</v>
       </c>
-      <c r="G15" s="3">
-        <v>13800</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
+        <v>27700</v>
+      </c>
+      <c r="J15" s="3">
         <v>27400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>27500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>26400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>12500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>12400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>25500</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1130,8 +1175,14 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,100 +1199,108 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>87700</v>
+      </c>
+      <c r="F17" s="3">
         <v>156500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>79100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>74600</v>
       </c>
-      <c r="G17" s="3">
-        <v>127000</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>126700</v>
+      </c>
+      <c r="J17" s="3">
         <v>74100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>76800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>76200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>71200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>73400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>119700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>700</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
+      <c r="R17" s="3">
+        <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-87900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-9600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-8600</v>
       </c>
-      <c r="G18" s="3">
-        <v>-64500</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-64300</v>
+      </c>
+      <c r="J18" s="3">
         <v>-8000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-5900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-7200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-6900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-5500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3700</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,8 +1313,14 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,16 +1340,18 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-5900</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1293,29 +1360,29 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>9700</v>
+      </c>
+      <c r="J20" s="3">
         <v>8400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>7400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>6600</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>2900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>2400</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1328,41 +1395,47 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-87900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-9200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>5500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-50600</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="J21" s="3">
         <v>14000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>15300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>12600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>5500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,47 +1454,53 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F22" s="3">
         <v>10600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>10400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>10200</v>
       </c>
-      <c r="G22" s="3">
-        <v>9200</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>19100</v>
+      </c>
+      <c r="J22" s="3">
         <v>16400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>14600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>13200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>7100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>5600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>10600</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1434,114 +1513,132 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-33900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-98500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-20000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-18900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-73700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-16100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-13100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-13800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-14000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-8200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-11900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-4900</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
+      <c r="R23" s="3">
+        <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F24" s="3">
         <v>-3100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="J24" s="3">
         <v>-1800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-2300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-2200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-2100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-3700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-3900</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,114 +1690,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-95400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-19500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-18500</v>
       </c>
-      <c r="G26" s="3">
-        <v>-71100</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-69600</v>
+      </c>
+      <c r="J26" s="3">
         <v>-14300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-10800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-11600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-12000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-8000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4900</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
+      <c r="R26" s="3">
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-95400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-19500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-18500</v>
       </c>
-      <c r="G27" s="3">
-        <v>-71100</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-69600</v>
+      </c>
+      <c r="J27" s="3">
         <v>-14300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-10800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-11600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-12000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-8300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-22900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4900</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
+      <c r="R27" s="3">
+        <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1867,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1926,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1985,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,16 +2044,22 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-2600</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1929,29 +2068,29 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="J32" s="3">
         <v>-8400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-7400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-6600</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-2900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-2400</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1964,61 +2103,73 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-95400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-19500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-18500</v>
       </c>
-      <c r="G33" s="3">
-        <v>-71100</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>-69600</v>
+      </c>
+      <c r="J33" s="3">
         <v>-14300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-10800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-11600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-12000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-8300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-22900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-4900</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
+      <c r="R33" s="3">
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,119 +2221,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-95400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-19500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-18500</v>
       </c>
-      <c r="G35" s="3">
-        <v>-71100</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>-69600</v>
+      </c>
+      <c r="J35" s="3">
         <v>-14300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-10800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-11600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-12000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-8300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-22900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-4900</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
+      <c r="R35" s="3">
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2371,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,61 +2394,69 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>29200</v>
+      </c>
+      <c r="F41" s="3">
         <v>19800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>22900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>30600</v>
       </c>
-      <c r="G41" s="3">
-        <v>34600</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>37500</v>
+      </c>
+      <c r="J41" s="3">
         <v>42900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>40400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>31900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>86000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>72700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2329,44 +2508,50 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>54500</v>
+      </c>
+      <c r="F43" s="3">
         <v>48600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>47400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>48500</v>
       </c>
-      <c r="G43" s="3">
-        <v>45000</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>46800</v>
+      </c>
+      <c r="J43" s="3">
         <v>41900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>51500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>58300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>52300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>56700</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2382,43 +2567,49 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F44" s="3">
         <v>9900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>7400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>8800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>10100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>8300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>9900</v>
-      </c>
-      <c r="J44" s="3">
-        <v>12100</v>
-      </c>
-      <c r="K44" s="3">
-        <v>15500</v>
       </c>
       <c r="L44" s="3">
         <v>12100</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
+      <c r="M44" s="3">
+        <v>15500</v>
+      </c>
+      <c r="N44" s="3">
+        <v>12100</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
@@ -2435,114 +2626,132 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F45" s="3">
         <v>13900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>11100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>12600</v>
       </c>
-      <c r="G45" s="3">
-        <v>13500</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>8900</v>
+      </c>
+      <c r="J45" s="3">
         <v>13300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>9100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>7700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>7400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>10500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
+      <c r="R45" s="3">
+        <v>0</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>102000</v>
+      </c>
+      <c r="F46" s="3">
         <v>92200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>88800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>100500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>103200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>106500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>110900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>110000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>161200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>152000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2700</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
+      <c r="R46" s="3">
+        <v>0</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2570,23 +2779,23 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
+      <c r="L47" s="3">
+        <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>259200</v>
-      </c>
-      <c r="N47" s="3">
-        <v>259200</v>
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>259200</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>259200</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>259200</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2594,44 +2803,50 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>20300</v>
+      </c>
+      <c r="F48" s="3">
         <v>22000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>22900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>21600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>21900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>22600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>19800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>21200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>12200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>12600</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,44 +2862,50 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>453200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>462600</v>
+      </c>
+      <c r="F49" s="3">
         <v>470600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>558300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>553100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>562200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>626900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>638000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>649500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>585400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>594800</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,8 +2921,14 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2980,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,61 +3039,73 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1300</v>
+        <v>4400</v>
       </c>
       <c r="E52" s="3">
-        <v>1300</v>
+        <v>2100</v>
       </c>
       <c r="F52" s="3">
         <v>1300</v>
       </c>
       <c r="G52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I52" s="3">
         <v>1400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>900</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3">
         <v>300</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,61 +3157,73 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>576600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>587000</v>
+      </c>
+      <c r="F54" s="3">
         <v>586200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>671300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>676500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>688700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>757500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>769400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>781400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>759600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>760400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>260400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>261500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>261800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>300</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3243,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,8 +3266,10 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3016,247 +3277,271 @@
         <v>22500</v>
       </c>
       <c r="E57" s="3">
+        <v>24000</v>
+      </c>
+      <c r="F57" s="3">
+        <v>22500</v>
+      </c>
+      <c r="G57" s="3">
         <v>21600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>23300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>17800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>18200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>19300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>19900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>16000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>20500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F58" s="3">
         <v>4300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>4800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>5400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5500</v>
       </c>
       <c r="H58" s="3">
         <v>5400</v>
       </c>
       <c r="I58" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K58" s="3">
         <v>3300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>3700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>48000</v>
+      </c>
+      <c r="F59" s="3">
         <v>36100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>27600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>26400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>25500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>23400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>25200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>21400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>28700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>33400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>4600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>72300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>74500</v>
+      </c>
+      <c r="F60" s="3">
         <v>62800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>54000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>55100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>48800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>47100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>47800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>44500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>48200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>57700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>300</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>437900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>437700</v>
+      </c>
+      <c r="F61" s="3">
         <v>412600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>412900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>413100</v>
-      </c>
-      <c r="G61" s="3">
-        <v>414000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>414800</v>
       </c>
       <c r="I61" s="3">
         <v>414000</v>
       </c>
       <c r="J61" s="3">
+        <v>414800</v>
+      </c>
+      <c r="K61" s="3">
         <v>414000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
+        <v>414000</v>
+      </c>
+      <c r="M61" s="3">
         <v>399400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>378700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3272,61 +3557,73 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>37800</v>
+      </c>
+      <c r="F62" s="3">
         <v>39600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>41400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>43700</v>
       </c>
-      <c r="G62" s="3">
-        <v>45200</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>70400</v>
+      </c>
+      <c r="J62" s="3">
         <v>44100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>43800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>47800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>39900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>40100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>23800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>18400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>21100</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3675,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3734,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,61 +3793,73 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>554300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>550000</v>
+      </c>
+      <c r="F66" s="3">
         <v>515100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>508200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>511800</v>
       </c>
-      <c r="G66" s="3">
-        <v>508100</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>508000</v>
+      </c>
+      <c r="J66" s="3">
         <v>506000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>505500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>506300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>487500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>476400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>29400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>21800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>22100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>300</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3879,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3934,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3993,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +4052,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,61 +4111,73 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-432900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-415300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-381600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-286200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-266700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-248200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-173000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-159900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-148800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-138200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-126200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-13600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-4900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-4900</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
+      <c r="R72" s="3">
+        <v>0</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4229,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4288,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,61 +4347,73 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F76" s="3">
         <v>71100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>163000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>164700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>180700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>251500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>263900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>275100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>272100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>284000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>231000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>239700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>239800</v>
       </c>
-      <c r="P76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
+      <c r="R76" s="3">
+        <v>0</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,119 +4465,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-95400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-19500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-18500</v>
       </c>
-      <c r="G81" s="3">
-        <v>-71100</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>-69600</v>
+      </c>
+      <c r="J81" s="3">
         <v>-14300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-10800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-11600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-12000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-8300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-22900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-4900</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
+      <c r="R81" s="3">
+        <v>0</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,41 +4615,43 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>13600</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>14100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>13800</v>
-      </c>
-      <c r="H83" s="3">
-        <v>13700</v>
       </c>
       <c r="I83" s="3">
         <v>13800</v>
       </c>
       <c r="J83" s="3">
+        <v>13700</v>
+      </c>
+      <c r="K83" s="3">
+        <v>13800</v>
+      </c>
+      <c r="L83" s="3">
         <v>13200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>12500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4267,14 +4664,20 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4729,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4788,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4847,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4906,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,61 +4965,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F89" s="3">
         <v>3200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-4200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>9800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>14700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-4000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-5300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-8200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,43 +5051,45 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-5400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-5400</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-4600</v>
       </c>
       <c r="H91" s="3">
         <v>-4800</v>
       </c>
       <c r="I91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-3400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-3600</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
@@ -4659,14 +5100,20 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +5165,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,41 +5224,47 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-5400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-5400</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-4600</v>
       </c>
       <c r="H94" s="3">
         <v>-4800</v>
       </c>
       <c r="I94" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-4700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-48500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-3600</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4818,14 +5277,20 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5310,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4898,8 +5365,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5424,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5483,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,41 +5542,47 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>22700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>22300</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5104,14 +5595,20 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5119,31 +5616,31 @@
         <v>-200</v>
       </c>
       <c r="E101" s="3">
+        <v>300</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -5157,63 +5654,75 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-7500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-4000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-8300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>8500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-54100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>13300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>63600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1900</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
   <si>
     <t>KORE</t>
   </si>
@@ -656,139 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E8" s="3">
         <v>76000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>72500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>68600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>69500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>66000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>62400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>66100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>70900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>69000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>64300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>67900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>116000</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -804,50 +808,53 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E9" s="3">
         <v>34200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>35500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>31000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>31700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>30300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>28700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>31500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>33600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>35300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>33500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>35000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>53700</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -863,50 +870,53 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E10" s="3">
         <v>41800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>37000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>37600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>37800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>35700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>33700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>34600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>37300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>33700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>30800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>32900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>62300</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,8 +932,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,8 +958,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1004,8 +1018,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,41 +1080,44 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>2600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>78300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>58100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1400</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1110,8 +1130,8 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1122,50 +1142,53 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E15" s="3">
         <v>13600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>15300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>14500</v>
       </c>
       <c r="G15" s="3">
         <v>14500</v>
       </c>
       <c r="H15" s="3">
+        <v>14500</v>
+      </c>
+      <c r="I15" s="3">
         <v>14100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>27700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>27400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>27500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>26400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>25500</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1181,8 +1204,11 @@
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,58 +1227,59 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E17" s="3">
         <v>83400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>87700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>156500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>79100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>74600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>126700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>74100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>76800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>76200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>71200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>73400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>119700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
@@ -1260,50 +1287,53 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-57100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-15200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-87900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-64300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3700</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,8 +1349,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,20 +1375,21 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E20" s="3">
         <v>2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5900</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1363,29 +1397,29 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>9700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6600</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>2900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2400</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1401,44 +1435,47 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-51600</v>
+      </c>
+      <c r="E21" s="3">
         <v>8800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-20300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-87900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-40800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5500</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1460,50 +1497,53 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E22" s="3">
         <v>13200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>19100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>10600</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1519,58 +1559,61 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-65700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-18000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-33900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-98500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-20000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-73700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4900</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
@@ -1578,58 +1621,61 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-4100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3900</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
@@ -1637,8 +1683,11 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,58 +1745,61 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-64300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-33700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-95400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-19500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-69600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4900</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
@@ -1755,58 +1807,61 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-64300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-33700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-95400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-19500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-18500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-69600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-22900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4900</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
@@ -1814,8 +1869,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,20 +2117,23 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5900</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2071,29 +2141,29 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-9700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6600</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-2900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2400</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2109,58 +2179,61 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-64300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-33700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-95400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-18500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-69600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-22900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4900</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
@@ -2168,8 +2241,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,58 +2303,61 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-64300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-33700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-95400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-18500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-69600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-22900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4900</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
@@ -2286,72 +2365,78 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,56 +2482,57 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E41" s="3">
         <v>25500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>29200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>42900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>86000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>72700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1900</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,8 +2542,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2514,47 +2604,50 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E43" s="3">
         <v>56300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>54500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>48600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>47400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>48500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>41900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>51500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>58300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>52300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>56700</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2573,47 +2666,50 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E44" s="3">
         <v>7600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>8200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>8800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2632,58 +2728,61 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E45" s="3">
         <v>9500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>700</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -2691,58 +2790,61 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>88200</v>
+      </c>
+      <c r="E46" s="3">
         <v>99000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>102000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>92200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>88800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>100500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>103200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>106500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>110900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>110000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>161200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>152000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2700</v>
       </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
+      <c r="S46" s="3">
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
@@ -2750,8 +2852,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2785,11 +2890,11 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
-        <v>259200</v>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>259200</v>
@@ -2797,8 +2902,8 @@
       <c r="Q47" s="3">
         <v>259200</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>259200</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -2809,47 +2914,50 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E48" s="3">
         <v>20100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12600</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2868,47 +2976,50 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>397400</v>
+      </c>
+      <c r="E49" s="3">
         <v>453200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>462600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>470600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>558300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>553100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>562200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>626900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>638000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>649500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>585400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>594800</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,8 +3038,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,19 +3162,22 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E52" s="3">
         <v>4400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1300</v>
       </c>
       <c r="G52" s="3">
         <v>1300</v>
@@ -3066,46 +3186,49 @@
         <v>1300</v>
       </c>
       <c r="I52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J52" s="3">
         <v>1400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>700</v>
-      </c>
-      <c r="L52" s="3">
-        <v>800</v>
       </c>
       <c r="M52" s="3">
         <v>800</v>
       </c>
       <c r="N52" s="3">
+        <v>800</v>
+      </c>
+      <c r="O52" s="3">
         <v>900</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3">
         <v>300</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,67 +3286,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>509800</v>
+      </c>
+      <c r="E54" s="3">
         <v>576600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>587000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>586200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>671300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>676500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>688700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>757500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>769400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>781400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>759600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>760400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>260400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>261500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>261800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>300</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,55 +3398,56 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E57" s="3">
         <v>22500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
+      <c r="R57" s="3">
+        <v>100</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
@@ -3327,8 +3458,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3336,215 +3470,224 @@
         <v>1900</v>
       </c>
       <c r="E58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F58" s="3">
         <v>2500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E59" s="3">
         <v>47900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>48000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>36100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>33400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E60" s="3">
         <v>72300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>74500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>62800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>54000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>55100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>48800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>47100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>47800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>44500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>48200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>57700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>300</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>438100</v>
+      </c>
+      <c r="E61" s="3">
         <v>437900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>437700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>412600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>412900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>413100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>414000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>414800</v>
-      </c>
-      <c r="K61" s="3">
-        <v>414000</v>
       </c>
       <c r="L61" s="3">
         <v>414000</v>
       </c>
       <c r="M61" s="3">
+        <v>414000</v>
+      </c>
+      <c r="N61" s="3">
         <v>399400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>378700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3563,56 +3706,59 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E62" s="3">
         <v>44100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>37800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>39600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>41400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>43700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>70400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>44100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>43800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>47800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>39900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>40100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>21100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,8 +3768,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,67 +3954,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>547600</v>
+      </c>
+      <c r="E66" s="3">
         <v>554300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>550000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>515100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>508200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>511800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>508000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>506000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>505500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>506300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>487500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>476400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>300</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,58 +4288,61 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-497200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-432900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-415300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-381600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-286200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-266700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-248200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-173000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-159900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-148800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-138200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-126200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-13600</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-4900</v>
       </c>
       <c r="Q72" s="3">
         <v>-4900</v>
       </c>
       <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+        <v>-4900</v>
+      </c>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4176,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,58 +4536,61 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E76" s="3">
         <v>22300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>37000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>71100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>163000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>164700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>180700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>251500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>263900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>275100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>272100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>284000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>231000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>239700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>239800</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -4412,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,122 +4660,128 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-64300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-33700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-95400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-18500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-69600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-22900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4900</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
@@ -4594,8 +4789,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,44 +4815,45 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>13600</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3">
         <v>14100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12500</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4670,14 +4869,17 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,58 +5185,61 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
@@ -5030,8 +5247,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,46 +5273,47 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4600</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-5400</v>
       </c>
       <c r="G91" s="3">
         <v>-5400</v>
       </c>
       <c r="H91" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-4800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3600</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -5106,14 +5327,17 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,44 +5457,47 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4600</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-5400</v>
       </c>
       <c r="G94" s="3">
         <v>-5400</v>
       </c>
       <c r="H94" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="I94" s="3">
         <v>-4800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-48500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5283,14 +5513,17 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5371,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,44 +5791,47 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>22700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1100</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-1300</v>
       </c>
       <c r="H100" s="3">
         <v>-1300</v>
       </c>
       <c r="I100" s="3">
-        <v>-1100</v>
+        <v>-1300</v>
       </c>
       <c r="J100" s="3">
         <v>-1100</v>
       </c>
       <c r="K100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L100" s="3">
         <v>-900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>22300</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5601,49 +5847,52 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
@@ -5660,69 +5909,75 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-54100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>13300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>63600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1900</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
   <si>
     <t>KORE</t>
   </si>
@@ -656,146 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E8" s="3">
         <v>67900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>76000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>72500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>68600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>69500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>66000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>62400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>66100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>70900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>69000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>64300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>67900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>116000</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,53 +815,56 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E9" s="3">
         <v>29200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>34200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>35500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>31000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>31700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>31500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>33600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>35300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>33500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>35000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>53700</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,53 +880,56 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>38700</v>
+        <v>38200</v>
       </c>
       <c r="E10" s="3">
+        <v>38600</v>
+      </c>
+      <c r="F10" s="3">
         <v>41800</v>
       </c>
-      <c r="F10" s="3">
-        <v>37000</v>
-      </c>
       <c r="G10" s="3">
+        <v>36900</v>
+      </c>
+      <c r="H10" s="3">
         <v>37600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>37800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>35700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>33700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>34600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>37300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>33700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>30800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>32900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>62300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,8 +972,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1021,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,44 +1100,47 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>45400</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
-        <v>2600</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>65900</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>78300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>58100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1133,8 +1153,8 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1145,53 +1165,56 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E15" s="3">
         <v>14400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>15300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>14500</v>
       </c>
       <c r="H15" s="3">
         <v>14500</v>
       </c>
       <c r="I15" s="3">
+        <v>14500</v>
+      </c>
+      <c r="J15" s="3">
         <v>14100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>27700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>27400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>27500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>26400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>25500</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,61 +1254,62 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>125000</v>
+        <v>74500</v>
       </c>
       <c r="E17" s="3">
+        <v>78700</v>
+      </c>
+      <c r="F17" s="3">
         <v>83400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>87700</v>
       </c>
-      <c r="G17" s="3">
-        <v>156500</v>
-      </c>
       <c r="H17" s="3">
+        <v>78200</v>
+      </c>
+      <c r="I17" s="3">
         <v>79100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>74600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>126700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>74100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>76800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>76200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>71200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>73400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>119700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>700</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+      <c r="T17" s="3">
+        <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
@@ -1290,53 +1317,56 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-57100</v>
+        <v>-5600</v>
       </c>
       <c r="E18" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7400</v>
       </c>
-      <c r="F18" s="3">
-        <v>-15200</v>
-      </c>
       <c r="G18" s="3">
-        <v>-87900</v>
+        <v>-15300</v>
       </c>
       <c r="H18" s="3">
         <v>-9600</v>
       </c>
       <c r="I18" s="3">
-        <v>-8600</v>
+        <v>-9600</v>
       </c>
       <c r="J18" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-64300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1382,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,53 +1409,54 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4700</v>
+        <v>1100</v>
       </c>
       <c r="E20" s="3">
-        <v>2600</v>
+        <v>-4100</v>
       </c>
       <c r="F20" s="3">
-        <v>-5900</v>
+        <v>-2000</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>9700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6600</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>2900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2400</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,47 +1472,50 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-51600</v>
+        <v>7500</v>
       </c>
       <c r="E21" s="3">
-        <v>8800</v>
+        <v>7700</v>
       </c>
       <c r="F21" s="3">
-        <v>-20300</v>
+        <v>8200</v>
       </c>
       <c r="G21" s="3">
-        <v>-87900</v>
+        <v>-7200</v>
       </c>
       <c r="H21" s="3">
-        <v>-9200</v>
+        <v>4500</v>
       </c>
       <c r="I21" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J21" s="3">
         <v>5500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-40800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,8 +1537,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1509,44 +1549,44 @@
         <v>13300</v>
       </c>
       <c r="E22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>12900</v>
+      </c>
+      <c r="G22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K22" s="3">
+        <v>19100</v>
+      </c>
+      <c r="L22" s="3">
+        <v>16400</v>
+      </c>
+      <c r="M22" s="3">
+        <v>14600</v>
+      </c>
+      <c r="N22" s="3">
         <v>13200</v>
       </c>
-      <c r="F22" s="3">
-        <v>12800</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="O22" s="3">
+        <v>7100</v>
+      </c>
+      <c r="P22" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Q22" s="3">
         <v>10600</v>
       </c>
-      <c r="H22" s="3">
-        <v>10400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>10200</v>
-      </c>
-      <c r="J22" s="3">
-        <v>19100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>16400</v>
-      </c>
-      <c r="L22" s="3">
-        <v>14600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>13200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>7100</v>
-      </c>
-      <c r="O22" s="3">
-        <v>5600</v>
-      </c>
-      <c r="P22" s="3">
-        <v>10600</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1562,61 +1602,64 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-65700</v>
+        <v>-19800</v>
       </c>
       <c r="E23" s="3">
+        <v>-85300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-18000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-33900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-98500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-20000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-18900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-73700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4900</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
@@ -1624,61 +1667,64 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-1400</v>
+        <v>-400</v>
       </c>
       <c r="E24" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
@@ -1686,8 +1732,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,61 +1797,64 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-64300</v>
+        <v>-19400</v>
       </c>
       <c r="E26" s="3">
+        <v>-83600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-17600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-33700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-95400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-19500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-18500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-69600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-11600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4900</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+      <c r="T26" s="3">
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
@@ -1810,61 +1862,64 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-64300</v>
+        <v>-19400</v>
       </c>
       <c r="E27" s="3">
+        <v>-83600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-17600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-33700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-95400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-18500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-69600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-22900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4900</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+      <c r="T27" s="3">
+        <v>0</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
@@ -1872,8 +1927,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,53 +2187,56 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4700</v>
+        <v>-1100</v>
       </c>
       <c r="E32" s="3">
-        <v>-2600</v>
+        <v>4100</v>
       </c>
       <c r="F32" s="3">
-        <v>5900</v>
+        <v>2000</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-7200</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-9700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6600</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-2900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,61 +2252,64 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-64300</v>
+        <v>-19400</v>
       </c>
       <c r="E33" s="3">
+        <v>-83600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-17600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-33700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-95400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-18500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-69600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-22900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4900</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
@@ -2244,8 +2317,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,61 +2382,64 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-64300</v>
+        <v>-19400</v>
       </c>
       <c r="E35" s="3">
+        <v>-83600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-17600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-33700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-95400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-18500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-69600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-22900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4900</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+      <c r="T35" s="3">
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
@@ -2368,75 +2447,81 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,59 +2569,60 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>23200</v>
+        <v>18600</v>
       </c>
       <c r="E41" s="3">
-        <v>25500</v>
+        <v>22300</v>
       </c>
       <c r="F41" s="3">
-        <v>29200</v>
+        <v>23000</v>
       </c>
       <c r="G41" s="3">
+        <v>27100</v>
+      </c>
+      <c r="H41" s="3">
         <v>19800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>42900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>31900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>86000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>72700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1900</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2632,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2554,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2607,8 +2697,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2616,41 +2709,41 @@
         <v>48200</v>
       </c>
       <c r="E43" s="3">
-        <v>56300</v>
+        <v>48300</v>
       </c>
       <c r="F43" s="3">
+        <v>58300</v>
+      </c>
+      <c r="G43" s="3">
         <v>54500</v>
       </c>
-      <c r="G43" s="3">
-        <v>48600</v>
-      </c>
       <c r="H43" s="3">
-        <v>47400</v>
+        <v>49800</v>
       </c>
       <c r="I43" s="3">
+        <v>48400</v>
+      </c>
+      <c r="J43" s="3">
         <v>48500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>46800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>41900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>51500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>58300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>52300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>56700</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2669,50 +2762,53 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E44" s="3">
         <v>7800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>8200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>10100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>15500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>12100</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2731,61 +2827,64 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>9000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>9500</v>
+        <v>800</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F45" s="3">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="G45" s="3">
-        <v>13900</v>
+        <v>4700</v>
       </c>
       <c r="H45" s="3">
-        <v>11100</v>
+        <v>3600</v>
       </c>
       <c r="I45" s="3">
-        <v>12600</v>
-      </c>
-      <c r="J45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>8900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
+      <c r="T45" s="3">
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
@@ -2793,61 +2892,64 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>88200</v>
+        <v>83500</v>
       </c>
       <c r="E46" s="3">
+        <v>86600</v>
+      </c>
+      <c r="F46" s="3">
         <v>99000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>102000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>92200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>88800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>100500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>103200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>106500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>110900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>110000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>161200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>152000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2700</v>
       </c>
-      <c r="S46" s="3">
-        <v>0</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
+      <c r="T46" s="3">
+        <v>0</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
@@ -2855,31 +2957,34 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2893,11 +2998,11 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3">
-        <v>259200</v>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>259200</v>
@@ -2905,8 +3010,8 @@
       <c r="R47" s="3">
         <v>259200</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>259200</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -2917,50 +3022,53 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E48" s="3">
         <v>19500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12600</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,50 +3087,53 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>397400</v>
+        <v>367600</v>
       </c>
       <c r="E49" s="3">
+        <v>376900</v>
+      </c>
+      <c r="F49" s="3">
         <v>453200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>462600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>470600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>558300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>553100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>562200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>626900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>638000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>649500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>585400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>594800</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,70 +3282,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E52" s="3">
         <v>4700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2100</v>
       </c>
-      <c r="G52" s="3">
-        <v>1300</v>
-      </c>
       <c r="H52" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="I52" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="J52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K52" s="3">
         <v>1400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>700</v>
-      </c>
-      <c r="M52" s="3">
-        <v>800</v>
       </c>
       <c r="N52" s="3">
         <v>800</v>
       </c>
       <c r="O52" s="3">
+        <v>800</v>
+      </c>
+      <c r="P52" s="3">
         <v>900</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3">
         <v>300</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,70 +3412,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>509800</v>
+        <v>473900</v>
       </c>
       <c r="E54" s="3">
+        <v>487700</v>
+      </c>
+      <c r="F54" s="3">
         <v>576600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>587000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>586200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>671300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>676500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>688700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>757500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>769400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>781400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>759600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>760400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>260400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>261500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>261800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>300</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,58 +3529,59 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E57" s="3">
         <v>21400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>22500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>100</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>100</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3461,236 +3592,248 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1900</v>
+        <v>3400</v>
       </c>
       <c r="E58" s="3">
-        <v>1900</v>
+        <v>3400</v>
       </c>
       <c r="F58" s="3">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="G58" s="3">
-        <v>4300</v>
+        <v>4000</v>
       </c>
       <c r="H58" s="3">
-        <v>4800</v>
+        <v>5700</v>
       </c>
       <c r="I58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K58" s="3">
+        <v>5500</v>
+      </c>
+      <c r="L58" s="3">
         <v>5400</v>
       </c>
-      <c r="J58" s="3">
-        <v>5500</v>
-      </c>
-      <c r="K58" s="3">
-        <v>5400</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>41700</v>
+        <v>21400</v>
       </c>
       <c r="E59" s="3">
-        <v>47900</v>
+        <v>21700</v>
       </c>
       <c r="F59" s="3">
-        <v>48000</v>
+        <v>24400</v>
       </c>
       <c r="G59" s="3">
-        <v>36100</v>
+        <v>26100</v>
       </c>
       <c r="H59" s="3">
-        <v>27600</v>
+        <v>10100</v>
       </c>
       <c r="I59" s="3">
-        <v>26400</v>
+        <v>9700</v>
       </c>
       <c r="J59" s="3">
+        <v>8900</v>
+      </c>
+      <c r="K59" s="3">
         <v>25500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>25200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>28700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>33400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>65000</v>
+        <v>64500</v>
       </c>
       <c r="E60" s="3">
+        <v>62600</v>
+      </c>
+      <c r="F60" s="3">
         <v>72300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>74500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>62800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>54000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>48800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>47100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>47800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>44500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>48200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>57700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>300</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>438100</v>
+        <v>447000</v>
       </c>
       <c r="E61" s="3">
-        <v>437900</v>
+        <v>447100</v>
       </c>
       <c r="F61" s="3">
-        <v>437700</v>
+        <v>447300</v>
       </c>
       <c r="G61" s="3">
-        <v>412600</v>
+        <v>447200</v>
       </c>
       <c r="H61" s="3">
-        <v>412900</v>
+        <v>422400</v>
       </c>
       <c r="I61" s="3">
-        <v>413100</v>
+        <v>422400</v>
       </c>
       <c r="J61" s="3">
+        <v>422100</v>
+      </c>
+      <c r="K61" s="3">
         <v>414000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>414800</v>
-      </c>
-      <c r="L61" s="3">
-        <v>414000</v>
       </c>
       <c r="M61" s="3">
         <v>414000</v>
       </c>
       <c r="N61" s="3">
+        <v>414000</v>
+      </c>
+      <c r="O61" s="3">
         <v>399400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>378700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3709,59 +3852,62 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>44600</v>
+        <v>33400</v>
       </c>
       <c r="E62" s="3">
+        <v>27700</v>
+      </c>
+      <c r="F62" s="3">
+        <v>22200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>14500</v>
+      </c>
+      <c r="H62" s="3">
+        <v>15700</v>
+      </c>
+      <c r="I62" s="3">
+        <v>12400</v>
+      </c>
+      <c r="J62" s="3">
+        <v>11400</v>
+      </c>
+      <c r="K62" s="3">
+        <v>70400</v>
+      </c>
+      <c r="L62" s="3">
         <v>44100</v>
       </c>
-      <c r="F62" s="3">
-        <v>37800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>39600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>41400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>43700</v>
-      </c>
-      <c r="J62" s="3">
-        <v>70400</v>
-      </c>
-      <c r="K62" s="3">
-        <v>44100</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>43800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>47800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>39900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>40100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>21100</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,70 +4112,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>547600</v>
+        <v>551200</v>
       </c>
       <c r="E66" s="3">
+        <v>544900</v>
+      </c>
+      <c r="F66" s="3">
         <v>554300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>550000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>515100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>508200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>511800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>508000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>506000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>505500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>506300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>487500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>476400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>22100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>300</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,61 +4462,64 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-497200</v>
+        <v>-535900</v>
       </c>
       <c r="E72" s="3">
+        <v>-516500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-432900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-415300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-381600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-286200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-266700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-248200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-173000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-159900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-148800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-138200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-126200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-13600</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-4900</v>
       </c>
       <c r="R72" s="3">
         <v>-4900</v>
       </c>
       <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+        <v>-4900</v>
+      </c>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,61 +4722,64 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-37800</v>
+        <v>-77200</v>
       </c>
       <c r="E76" s="3">
+        <v>-57200</v>
+      </c>
+      <c r="F76" s="3">
         <v>22300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>37000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>71100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>163000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>164700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>180700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>251500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>263900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>275100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>272100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>284000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>231000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>239700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>239800</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,128 +4852,134 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-64300</v>
+        <v>-19400</v>
       </c>
       <c r="E81" s="3">
+        <v>-83600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-17600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-33700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-95400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-18500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-69600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-22900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4900</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+      <c r="T81" s="3">
+        <v>0</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
@@ -4792,8 +4987,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,47 +5014,48 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>14500</v>
       </c>
       <c r="E83" s="3">
-        <v>13600</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+        <v>14000</v>
+      </c>
+      <c r="F83" s="3">
+        <v>14700</v>
+      </c>
+      <c r="G83" s="3">
+        <v>16100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>13700</v>
       </c>
       <c r="I83" s="3">
-        <v>14100</v>
+        <v>13800</v>
       </c>
       <c r="J83" s="3">
+        <v>13200</v>
+      </c>
+      <c r="K83" s="3">
         <v>13800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12500</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4872,14 +5071,17 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,61 +5402,64 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>4000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-800</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
@@ -5250,8 +5467,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,49 +5494,50 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4100</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
-        <v>-4700</v>
+        <v>-900</v>
       </c>
       <c r="F91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-4600</v>
       </c>
-      <c r="G91" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="L91" s="3">
         <v>-4800</v>
       </c>
-      <c r="J91" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3600</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -5330,14 +5551,17 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,47 +5687,50 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4600</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-5400</v>
       </c>
       <c r="H94" s="3">
         <v>-5400</v>
       </c>
       <c r="I94" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="J94" s="3">
         <v>-4800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-48500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3600</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5516,14 +5746,17 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,31 +5779,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,47 +6037,50 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>22700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-1300</v>
       </c>
       <c r="I100" s="3">
         <v>-1300</v>
       </c>
       <c r="J100" s="3">
-        <v>-1100</v>
+        <v>-1300</v>
       </c>
       <c r="K100" s="3">
         <v>-1100</v>
       </c>
       <c r="L100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M100" s="3">
         <v>-900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>22300</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5850,52 +6096,55 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>-200</v>
-      </c>
       <c r="F101" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G101" s="3">
-        <v>-200</v>
+        <v>1600</v>
       </c>
       <c r="H101" s="3">
-        <v>-100</v>
+        <v>-1400</v>
       </c>
       <c r="I101" s="3">
-        <v>200</v>
+        <v>-500</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>1600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
@@ -5912,72 +6161,78 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-54100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>63600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1900</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
   <si>
     <t>KORE</t>
   </si>
@@ -656,156 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>73300</v>
+      </c>
+      <c r="F8" s="3">
         <v>68900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>67900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>76000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>72500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>68600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>69500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>66000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>62400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>66100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>70900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>69000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>64300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>67900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>116000</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -818,59 +825,65 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>32000</v>
+      </c>
+      <c r="F9" s="3">
         <v>30700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>29200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>34200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>35500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>31000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>31700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>30300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>28700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>31500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>33600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>35300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>33500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>35000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>53700</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -883,59 +896,65 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>41300</v>
+      </c>
+      <c r="F10" s="3">
         <v>38200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>38600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>41800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>36900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>37600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>37800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>35700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>33700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>34600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>37300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>33700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>30800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>32900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>62300</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -948,8 +967,14 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,8 +998,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1038,8 +1065,14 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,8 +1136,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1112,41 +1151,41 @@
         <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>65900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J14" s="3">
         <v>78300</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>58100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1400</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1156,11 +1195,11 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1168,59 +1207,65 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F15" s="3">
         <v>14200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>14400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>13600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>15300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>14500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>14500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>14100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>27700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>27400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>27500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>26400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>12500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>12400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>25500</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1233,8 +1278,14 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,124 +1306,132 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>86400</v>
+      </c>
+      <c r="F17" s="3">
         <v>74500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>78700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>83400</v>
       </c>
-      <c r="G17" s="3">
-        <v>87700</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>85100</v>
+      </c>
+      <c r="J17" s="3">
         <v>78200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>79100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>74600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>126700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>74100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>76800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>76200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>71200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>73400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>119700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>700</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
+      <c r="V17" s="3">
+        <v>0</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-10800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-7400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-15300</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-9600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-9600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-8700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-64300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-8000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-7200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-6900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3700</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1385,8 +1444,14 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,59 +1475,61 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-4100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-2000</v>
       </c>
-      <c r="G20" s="3">
-        <v>7200</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>6600</v>
+      </c>
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>9700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>8400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>7400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>6600</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>2900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>2400</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1475,53 +1542,59 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F21" s="3">
         <v>7500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>7700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>8200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J21" s="3">
         <v>4500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>4700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>5500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-40800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>14000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>15300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>12600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>5500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,59 +1613,65 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E22" s="3">
         <v>13300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
+        <v>13300</v>
+      </c>
+      <c r="G22" s="3">
         <v>13000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>12900</v>
       </c>
-      <c r="G22" s="3">
-        <v>12000</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>12100</v>
+      </c>
+      <c r="J22" s="3">
         <v>10500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>10300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>10300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>19100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>16400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>14600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>13200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>7100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>5600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>10600</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1605,138 +1684,156 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-28900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-19800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-85300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-18000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-33900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-98500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-20000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-18900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-73700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-16100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-13100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-13800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-14000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-11900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-4900</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
+      <c r="V23" s="3">
+        <v>0</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-400</v>
+        <v>1100</v>
       </c>
       <c r="E24" s="3">
-        <v>-1700</v>
+        <v>-3500</v>
       </c>
       <c r="F24" s="3">
         <v>-400</v>
       </c>
       <c r="G24" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-3100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-4100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-2300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-2200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-2100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-3900</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,138 +1897,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-19400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-83600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-17600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-33700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-95400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-19500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-18500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-69600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-14300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-10800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-11600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-12000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-8000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-4900</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
+      <c r="V26" s="3">
+        <v>0</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-19400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-83600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-17600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-33700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-95400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-19500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-18500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-69600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-14300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-10800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-11600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-12000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-22900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-4900</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
+      <c r="V27" s="3">
+        <v>0</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2110,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2181,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2252,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,59 +2323,65 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>4100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>2000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-9700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-8400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-7400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-6600</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-2400</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2255,73 +2394,85 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-19400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-83600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-17600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-33700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-95400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-19500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-18500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-69600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-14300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-10800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-11600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-12000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-22900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-4900</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
+      <c r="V33" s="3">
+        <v>0</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,143 +2536,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-19400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-83600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-17600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-33700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-95400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-19500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-18500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-69600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-14300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-10800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-11600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-12000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-22900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-4900</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
+      <c r="V35" s="3">
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2714,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,73 +2741,81 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F41" s="3">
         <v>18600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>22300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>23000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>27100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>19800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>22900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>30600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>37500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>42900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>40400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>31900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>86000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>72700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1900</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2644,14 +2823,14 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>1000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2700,56 +2879,62 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>46800</v>
+      </c>
+      <c r="F43" s="3">
         <v>48200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>48300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>58300</v>
       </c>
-      <c r="G43" s="3">
-        <v>54500</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>57200</v>
+      </c>
+      <c r="J43" s="3">
         <v>49800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>48400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>48500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>46800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>41900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>51500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>58300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>52300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>56700</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2765,55 +2950,61 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>7600</v>
+        <v>6100</v>
       </c>
       <c r="E44" s="3">
-        <v>7800</v>
+        <v>6700</v>
       </c>
       <c r="F44" s="3">
         <v>7600</v>
       </c>
       <c r="G44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="H44" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I44" s="3">
         <v>8200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>9900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>7400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>8800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>10100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>8300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>9900</v>
-      </c>
-      <c r="N44" s="3">
-        <v>12100</v>
-      </c>
-      <c r="O44" s="3">
-        <v>15500</v>
       </c>
       <c r="P44" s="3">
         <v>12100</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
+      <c r="Q44" s="3">
+        <v>15500</v>
+      </c>
+      <c r="R44" s="3">
+        <v>12100</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
@@ -2830,138 +3021,156 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>2500</v>
       </c>
-      <c r="G45" s="3">
-        <v>4700</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J45" s="3">
         <v>3600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1800</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>8900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>13300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>9100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>7700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>7400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>10500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>700</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
+      <c r="V45" s="3">
+        <v>0</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>80000</v>
+      </c>
+      <c r="F46" s="3">
         <v>83500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>86600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>99000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>102000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>92200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>88800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>100500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>103200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>106500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>110900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>110000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>161200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>152000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2700</v>
       </c>
-      <c r="T46" s="3">
-        <v>0</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
+      <c r="V46" s="3">
+        <v>0</v>
       </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2986,11 +3195,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3001,23 +3210,23 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>0</v>
       </c>
       <c r="Q47" s="3">
-        <v>259200</v>
-      </c>
-      <c r="R47" s="3">
-        <v>259200</v>
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>259200</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>259200</v>
+      </c>
+      <c r="U47" s="3">
+        <v>259200</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3025,56 +3234,62 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>17500</v>
+      </c>
+      <c r="F48" s="3">
         <v>18400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>19500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>20100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>20300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>22000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>22900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>21600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>21900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>22600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>19800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>21200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>12200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>12600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3090,56 +3305,62 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>343900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>353900</v>
+      </c>
+      <c r="F49" s="3">
         <v>367600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>376900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>453200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>462600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>470600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>558300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>553100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>562200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>626900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>638000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>649500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>585400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>594800</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3155,8 +3376,14 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3447,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,8 +3518,14 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3294,64 +3533,70 @@
         <v>4500</v>
       </c>
       <c r="E52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G52" s="3">
         <v>4700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>4400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1200</v>
       </c>
       <c r="J52" s="3">
         <v>1200</v>
       </c>
       <c r="K52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M52" s="3">
         <v>1400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>900</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3">
         <v>300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,73 +3660,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>445100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>455800</v>
+      </c>
+      <c r="F54" s="3">
         <v>473900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>487700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>576600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>587000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>586200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>671300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>676500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>688700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>757500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>769400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>781400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>759600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>760400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>260400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>261500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>261800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>300</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3762,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,316 +3789,342 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F57" s="3">
         <v>22700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>21400</v>
-      </c>
-      <c r="F57" s="3">
-        <v>22500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>24000</v>
       </c>
       <c r="H57" s="3">
         <v>22500</v>
       </c>
       <c r="I57" s="3">
+        <v>24000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>22500</v>
+      </c>
+      <c r="K57" s="3">
         <v>21600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>23300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>17800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>18200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>19300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>19900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>16000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>20500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F58" s="3">
         <v>3400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3500</v>
       </c>
-      <c r="G58" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J58" s="3">
         <v>5700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>6300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>7000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>5500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>3300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>25700</v>
+      </c>
+      <c r="F59" s="3">
         <v>21400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>21700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>24400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>26100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>10100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>9700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>8900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>25500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>23400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>25200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>21400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>28700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>33400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>4600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>200</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>66100</v>
+      </c>
+      <c r="F60" s="3">
         <v>64500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>62600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>72300</v>
       </c>
-      <c r="G60" s="3">
-        <v>74500</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>72000</v>
+      </c>
+      <c r="J60" s="3">
         <v>62800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>54000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>55100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>48800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>47100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>47800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>44500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>48200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>57700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>5600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>300</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>446700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>446700</v>
+      </c>
+      <c r="F61" s="3">
         <v>447000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>447100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>447300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>447200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>422400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>422400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>422100</v>
-      </c>
-      <c r="K61" s="3">
-        <v>414000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>414800</v>
       </c>
       <c r="M61" s="3">
         <v>414000</v>
       </c>
       <c r="N61" s="3">
+        <v>414800</v>
+      </c>
+      <c r="O61" s="3">
         <v>414000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
+        <v>414000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>399400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>378700</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3855,73 +4140,85 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>38500</v>
+      </c>
+      <c r="F62" s="3">
         <v>33400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>27700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>22200</v>
       </c>
-      <c r="G62" s="3">
-        <v>14500</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>17100</v>
+      </c>
+      <c r="J62" s="3">
         <v>15700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>12400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>11400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>70400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>44100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>43800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>47800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>39900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>40100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>23800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>18400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>21100</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4282,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4353,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,73 +4424,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>560000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>555400</v>
+      </c>
+      <c r="F66" s="3">
         <v>551200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>544900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>554300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>550000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>515100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>508200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>511800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>508000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>506000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>505500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>506300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>487500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>476400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>29400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>21800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>22100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>300</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4526,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4593,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4664,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4400,8 +4735,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,73 +4806,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-576300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-561400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-535900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-516500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-432900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-415300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-381600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-286200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-266700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-248200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-173000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-159900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-148800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-138200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-126200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-13600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-4900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-4900</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
+      <c r="V72" s="3">
+        <v>0</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4948,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +5019,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,73 +5090,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-114900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-99600</v>
+      </c>
+      <c r="F76" s="3">
         <v>-77200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-57200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>22300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>37000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>71100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>163000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>164700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>180700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>251500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>263900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>275100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>272100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>284000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>231000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>239700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>239800</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
+      <c r="V76" s="3">
+        <v>0</v>
       </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,143 +5232,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-19400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-83600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-17600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-33700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-95400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-19500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-18500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-69600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-14300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-10800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-11600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-12000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-22900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-4900</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
+      <c r="V81" s="3">
+        <v>0</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,53 +5410,55 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>17600</v>
+      </c>
+      <c r="F83" s="3">
         <v>14500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>14000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>14700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>16100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>13700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>13800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>13200</v>
       </c>
       <c r="K83" s="3">
         <v>13800</v>
       </c>
       <c r="L83" s="3">
-        <v>13700</v>
+        <v>13200</v>
       </c>
       <c r="M83" s="3">
         <v>13800</v>
       </c>
       <c r="N83" s="3">
+        <v>13700</v>
+      </c>
+      <c r="O83" s="3">
+        <v>13800</v>
+      </c>
+      <c r="P83" s="3">
         <v>13200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>12500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5074,14 +5471,20 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5548,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5619,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5690,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5761,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,73 +5832,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F89" s="3">
         <v>1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>4000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-10900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>3200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-4200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>9800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>14700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-4000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-5300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-800</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,55 +5934,57 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-900</v>
       </c>
       <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-4600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-4800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-3800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-3400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-3600</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5554,14 +5995,20 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +6072,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,53 +6143,59 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-4100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-4700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-4600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-5400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-5400</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-4600</v>
       </c>
       <c r="L94" s="3">
         <v>-4800</v>
       </c>
       <c r="M94" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="O94" s="3">
         <v>-4700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-48500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3600</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5749,14 +6208,20 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6245,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5806,11 +6273,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5845,8 +6312,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6383,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6454,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,53 +6525,59 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>22700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>22300</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6099,14 +6590,20 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6114,43 +6611,43 @@
         <v>-200</v>
       </c>
       <c r="E101" s="3">
+        <v>300</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -6164,75 +6661,87 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-4100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>7400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-3400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-7500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-8300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>8500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-54100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>13300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>63600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1900</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>KORE</t>
   </si>
@@ -656,166 +656,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>71300</v>
+      </c>
+      <c r="E8" s="3">
         <v>72100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>73300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>68900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>67900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>76000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>72500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>68600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>69500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>66000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>62400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>66100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>70900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>69000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>64300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>67900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>116000</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,62 +835,65 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E9" s="3">
         <v>33000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>32000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>30700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>29200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>34200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>35500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>31000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>31700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>31500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>33600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>35300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>33500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>35000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>53700</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -902,62 +909,65 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E10" s="3">
         <v>39100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>41300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>38200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>38600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>41800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>36900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>37600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>37800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>35700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>33700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>34600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>37300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>33700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>30800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>32900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>62300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -973,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,8 +1013,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1071,8 +1085,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,53 +1159,56 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="D14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>65900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>2600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>78300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>58100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1400</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1201,8 +1221,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1213,62 +1233,65 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E15" s="3">
         <v>13900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>14000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>15300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>14500</v>
       </c>
       <c r="K15" s="3">
         <v>14500</v>
       </c>
       <c r="L15" s="3">
+        <v>14500</v>
+      </c>
+      <c r="M15" s="3">
         <v>14100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>27700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>27400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>27500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>26400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>12500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>12400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>25500</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,70 +1334,71 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E17" s="3">
         <v>74600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>86400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>74500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>78700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>83400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>85100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>78200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>79100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>74600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>126700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>74100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>76800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>76200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>71200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>73400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>119700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>700</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+      <c r="W17" s="3">
+        <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
@@ -1379,62 +1406,65 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-9600</v>
       </c>
       <c r="K18" s="3">
         <v>-9600</v>
       </c>
       <c r="L18" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="M18" s="3">
         <v>-8700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-64300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3700</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1450,8 +1480,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,62 +1510,63 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>9700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6600</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>2900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2400</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,56 +1582,59 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E21" s="3">
         <v>12900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-40800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,62 +1656,65 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E22" s="3">
         <v>13000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>13300</v>
       </c>
       <c r="F22" s="3">
         <v>13300</v>
       </c>
       <c r="G22" s="3">
+        <v>13300</v>
+      </c>
+      <c r="H22" s="3">
         <v>13000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10500</v>
-      </c>
-      <c r="K22" s="3">
-        <v>10300</v>
       </c>
       <c r="L22" s="3">
         <v>10300</v>
       </c>
       <c r="M22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="N22" s="3">
         <v>19100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>13200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>10600</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1690,70 +1730,73 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-28900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-85300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-33900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-98500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-20000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-73700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4900</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
+      <c r="W23" s="3">
+        <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
@@ -1761,70 +1804,73 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3900</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,70 +1952,73 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-83600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-33700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-95400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-19500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-69600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4900</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+      <c r="W26" s="3">
+        <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
@@ -1974,70 +2026,73 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-83600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-33700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-95400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-69600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-22900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4900</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
+      <c r="W27" s="3">
+        <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
@@ -2045,8 +2100,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,62 +2396,65 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-9700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-2900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2400</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2400,70 +2470,73 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-83600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-33700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-95400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-69600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-12000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-22900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4900</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
+      <c r="W33" s="3">
+        <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
@@ -2471,8 +2544,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,70 +2618,73 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-83600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-33700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-95400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-69600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-12000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-22900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4900</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
+      <c r="W35" s="3">
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
@@ -2613,84 +2692,90 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,68 +2829,69 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E41" s="3">
         <v>19700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>27100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>22900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>37500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>40400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>31900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>86000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>72700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1900</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,8 +2901,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2829,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -2885,59 +2975,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>45400</v>
+        <v>46400</v>
       </c>
       <c r="E43" s="3">
+        <v>48400</v>
+      </c>
+      <c r="F43" s="3">
         <v>46800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>48200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>48300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>58300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>57200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>49800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>48400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>48500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>46800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>41900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>51500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>58300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>52300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>56700</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2956,59 +3049,62 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E44" s="3">
         <v>6100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>12100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>15500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>12100</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,70 +3123,73 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>1600</v>
       </c>
       <c r="E45" s="3">
         <v>1600</v>
       </c>
       <c r="F45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I45" s="3">
         <v>2500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>8900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>700</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
+      <c r="W45" s="3">
+        <v>0</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
@@ -3098,70 +3197,73 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>79200</v>
+      </c>
+      <c r="E46" s="3">
         <v>80500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>80000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>83500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>86600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>99000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>102000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>92200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>88800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>100500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>103200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>106500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>110900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>110000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>161200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>152000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2700</v>
       </c>
-      <c r="V46" s="3">
-        <v>0</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
+      <c r="W46" s="3">
+        <v>0</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
@@ -3169,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3201,8 +3306,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3216,11 +3321,11 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3">
-        <v>259200</v>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3">
         <v>259200</v>
@@ -3228,8 +3333,8 @@
       <c r="U47" s="3">
         <v>259200</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
+      <c r="V47" s="3">
+        <v>259200</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
@@ -3240,59 +3345,62 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E48" s="3">
         <v>16200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12600</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3311,59 +3419,62 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>333000</v>
+      </c>
+      <c r="E49" s="3">
         <v>343900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>353900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>367600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>376900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>453200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>462600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>470600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>558300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>553100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>562200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>626900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>638000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>649500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>585400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>594800</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,13 +3641,16 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4500</v>
+        <v>5900</v>
       </c>
       <c r="E52" s="3">
         <v>4500</v>
@@ -3539,16 +3659,16 @@
         <v>4500</v>
       </c>
       <c r="G52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="H52" s="3">
         <v>4700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1200</v>
       </c>
       <c r="K52" s="3">
         <v>1200</v>
@@ -3557,46 +3677,49 @@
         <v>1200</v>
       </c>
       <c r="M52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N52" s="3">
         <v>1400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>700</v>
-      </c>
-      <c r="P52" s="3">
-        <v>800</v>
       </c>
       <c r="Q52" s="3">
         <v>800</v>
       </c>
       <c r="R52" s="3">
+        <v>800</v>
+      </c>
+      <c r="S52" s="3">
         <v>900</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3">
         <v>300</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,79 +3789,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>432900</v>
+      </c>
+      <c r="E54" s="3">
         <v>445100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>455800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>473900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>487700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>576600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>587000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>586200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>671300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>676500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>688700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>757500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>769400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>781400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>759600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>760400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>260400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>261500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>261800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>300</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,67 +3921,68 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E57" s="3">
         <v>18600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>21600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>23300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>19900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>200</v>
-      </c>
-      <c r="T57" s="3">
-        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
+      <c r="V57" s="3">
+        <v>100</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
@@ -3862,272 +3993,284 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3300</v>
+        <v>3100</v>
       </c>
       <c r="E58" s="3">
         <v>3300</v>
       </c>
       <c r="F58" s="3">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="G58" s="3">
         <v>3400</v>
       </c>
       <c r="H58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I58" s="3">
         <v>3500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>14300</v>
+        <v>25300</v>
       </c>
       <c r="E59" s="3">
+        <v>22300</v>
+      </c>
+      <c r="F59" s="3">
         <v>25700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>23400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>25200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>28700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>33400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>200</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E60" s="3">
         <v>65400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>66100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>64500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>62600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>72300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>72000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>62800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>54000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>55100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>48800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>47100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>44500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>48200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>57700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>300</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>446700</v>
+        <v>444900</v>
       </c>
       <c r="E61" s="3">
         <v>446700</v>
       </c>
       <c r="F61" s="3">
+        <v>446700</v>
+      </c>
+      <c r="G61" s="3">
         <v>447000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>447100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>447300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>447200</v>
-      </c>
-      <c r="J61" s="3">
-        <v>422400</v>
       </c>
       <c r="K61" s="3">
         <v>422400</v>
       </c>
       <c r="L61" s="3">
+        <v>422400</v>
+      </c>
+      <c r="M61" s="3">
         <v>422100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>414000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>414800</v>
-      </c>
-      <c r="O61" s="3">
-        <v>414000</v>
       </c>
       <c r="P61" s="3">
         <v>414000</v>
       </c>
       <c r="Q61" s="3">
+        <v>414000</v>
+      </c>
+      <c r="R61" s="3">
         <v>399400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>378700</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4146,68 +4289,71 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E62" s="3">
         <v>44600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>38500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>27700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>70400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>44100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>43800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>47800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>39900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>40100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,79 +4585,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>566400</v>
+      </c>
+      <c r="E66" s="3">
         <v>560000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>555400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>551200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>544900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>554300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>550000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>515100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>508200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>511800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>508000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>506000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>505500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>506300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>487500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>476400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>21800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>22100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>300</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,70 +4983,73 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-593100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-576300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-561400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-535900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-516500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-432900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-415300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-381600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-286200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-266700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-248200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-173000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-159900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-148800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-138200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-126200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-13600</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-4900</v>
       </c>
       <c r="U72" s="3">
         <v>-4900</v>
       </c>
       <c r="V72" s="3">
-        <v>0</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
+        <v>-4900</v>
+      </c>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,70 +5279,73 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-133500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-114900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-99600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-77200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-57200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>37000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>71100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>163000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>164700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>180700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>251500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>263900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>275100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>272100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>284000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>231000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>239700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>239800</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
+      <c r="W76" s="3">
+        <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,146 +5427,152 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-83600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-33700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-95400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-69600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-12000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-22900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4900</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
+      <c r="W81" s="3">
+        <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
@@ -5385,8 +5580,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,56 +5610,57 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F83" s="3">
+        <v>17600</v>
+      </c>
+      <c r="G83" s="3">
+        <v>14500</v>
+      </c>
+      <c r="H83" s="3">
         <v>14000</v>
       </c>
-      <c r="E83" s="3">
-        <v>17600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>14500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>14000</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12500</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5477,14 +5676,17 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,70 +6052,73 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E89" s="3">
         <v>2900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-800</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
@@ -5909,8 +6126,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,58 +6156,59 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-900</v>
       </c>
       <c r="H91" s="3">
         <v>-900</v>
       </c>
       <c r="I91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3600</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -6001,14 +6222,17 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,56 +6376,59 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4600</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-5400</v>
       </c>
       <c r="K94" s="3">
         <v>-5400</v>
       </c>
       <c r="L94" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="M94" s="3">
         <v>-4800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-48500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3600</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6214,14 +6444,17 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6279,8 +6513,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,56 +6774,59 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>22700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-1300</v>
       </c>
       <c r="L100" s="3">
         <v>-1300</v>
       </c>
       <c r="M100" s="3">
-        <v>-1100</v>
+        <v>-1300</v>
       </c>
       <c r="N100" s="3">
         <v>-1100</v>
       </c>
       <c r="O100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P100" s="3">
         <v>-900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>22300</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6596,61 +6842,64 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>1600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
@@ -6667,81 +6916,87 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-54100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>13300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>63600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1900</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KORE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
   <si>
     <t>KORE</t>
   </si>
@@ -656,183 +656,190 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>73900</v>
+      </c>
+      <c r="F8" s="3">
         <v>68700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>71300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>72100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>73300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>68900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>67900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>76000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>72500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>68600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>69500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>66000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>62400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>66100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>70900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>69000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>64300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>67900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>116000</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -845,71 +852,77 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>32300</v>
+      </c>
+      <c r="F9" s="3">
         <v>30700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>31900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>33000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>32000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>30700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>29200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>34200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>35500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>31000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>31700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>30300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>28700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>31500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>33600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>35300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>33500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>35000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>53700</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,71 +935,77 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>41500</v>
+      </c>
+      <c r="F10" s="3">
         <v>37900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>39300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>39100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>41300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>38200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>38600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>41800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>36900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>37600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>37800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>35700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>33700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>34600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>37300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>33700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>30800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>32900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>62300</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -999,8 +1018,14 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,8 +1053,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1105,8 +1132,14 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,8 +1215,14 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1191,53 +1230,53 @@
         <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>1100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>65900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>2600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>78300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>58100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>1400</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1247,11 +1286,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1259,71 +1298,77 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E15" s="3">
         <v>13700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
+        <v>13700</v>
+      </c>
+      <c r="G15" s="3">
         <v>13600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>13900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>14000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>14200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>14400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>13600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>15300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>14500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>14500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>14100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>27700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>27400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>27500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>26400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>12500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>12400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>25500</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1336,8 +1381,14 @@
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,148 +1413,156 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>69900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>74500</v>
+      </c>
+      <c r="F17" s="3">
         <v>72900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>76500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>74600</v>
       </c>
-      <c r="G17" s="3">
-        <v>86400</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>84400</v>
+      </c>
+      <c r="J17" s="3">
         <v>74500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>78700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>83400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>85100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>78200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>79100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>74600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>126700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>74100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>76800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>76200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>71200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>73400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>119700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>700</v>
       </c>
-      <c r="X17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
+      <c r="Z17" s="3">
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-5200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-13100</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-5600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-10800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-7400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-12700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-9600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-9600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-8700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-64300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-5900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-7200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-6900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-5500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-3700</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1516,8 +1575,14 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,71 +1610,73 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-4100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>6600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>9700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>8400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>7400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>6600</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>2400</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1622,65 +1689,71 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F21" s="3">
         <v>9800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>12400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>12900</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>100</v>
+      </c>
+      <c r="J21" s="3">
         <v>7500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>7700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>8200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-4000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>4500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>5500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-40800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>14000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>15300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>12600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>5500</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,71 +1772,77 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F22" s="3">
         <v>13500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>13200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>13000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>13300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>13300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>13000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>12900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>12100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>10500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>10300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>10300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>19100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>16400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>14600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>13200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>7100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>5600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>10600</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1776,162 +1855,180 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-17300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-15400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-13800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-28900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-19800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-85300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-18000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-33900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-98500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-20000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-18900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-73700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-13100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-13800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-14000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-8200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-11900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-4900</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
+      <c r="Z23" s="3">
+        <v>0</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="F24" s="3">
         <v>-4600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-3500</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-1700</v>
       </c>
       <c r="J24" s="3">
         <v>-400</v>
       </c>
       <c r="K24" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-3100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-4100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-2300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-2200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-2100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-3700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-3900</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2104,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-12700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-16900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-14900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-25400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-19400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-83600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-17600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-33700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-95400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-19500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-18500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-69600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-10800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-11600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-12000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-4500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-8000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-4900</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
+      <c r="Z26" s="3">
+        <v>0</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-12700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-16900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-14900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-25400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-19400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-83600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-17600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-33700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-95400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-19500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-18500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-69600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-10800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-11600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-12000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-8300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-22900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-4900</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
+      <c r="Z27" s="3">
+        <v>0</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2353,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,8 +2436,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2519,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,71 +2602,77 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>4100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-6600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-9700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-7400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-6600</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-2400</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,85 +2685,97 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-12700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-16900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-14900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-25400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-19400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-83600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-17600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-33700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-95400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-19500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-18500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-69600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-10800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-11600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-12000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-8300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-22900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-4900</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
+      <c r="Z33" s="3">
+        <v>0</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2851,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-12700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-16900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-14900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-25400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-19400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-83600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-17600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-33700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-95400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-19500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-18500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-69600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-10800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-11600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-12000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-8300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-22900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-4900</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
+      <c r="Z35" s="3">
+        <v>0</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +3057,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,85 +3088,93 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>26700</v>
+      </c>
+      <c r="F41" s="3">
         <v>19300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>21000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>19700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>19400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>18600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>22300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>23000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>27100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>19800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>22900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>30600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>37500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>42900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>40400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>31900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>86000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>72700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1900</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3071,68 +3250,74 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>50100</v>
+      </c>
+      <c r="F43" s="3">
         <v>49900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>46400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>48400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>46800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>48200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>48300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>58300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>57200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>49800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>48400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>48500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>46800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>41900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>51500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>58300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>52300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>56700</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3148,67 +3333,73 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F44" s="3">
         <v>7400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>6100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>6700</v>
-      </c>
-      <c r="H44" s="3">
-        <v>7600</v>
-      </c>
-      <c r="I44" s="3">
-        <v>7800</v>
       </c>
       <c r="J44" s="3">
         <v>7600</v>
       </c>
       <c r="K44" s="3">
+        <v>7800</v>
+      </c>
+      <c r="L44" s="3">
+        <v>7600</v>
+      </c>
+      <c r="M44" s="3">
         <v>8200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>9900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>7400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>8800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>10100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>8300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>9900</v>
-      </c>
-      <c r="R44" s="3">
-        <v>12100</v>
-      </c>
-      <c r="S44" s="3">
-        <v>15500</v>
       </c>
       <c r="T44" s="3">
         <v>12100</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
+      <c r="U44" s="3">
+        <v>15500</v>
+      </c>
+      <c r="V44" s="3">
+        <v>12100</v>
       </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
@@ -3225,162 +3416,180 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>900</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E45" s="3">
         <v>1600</v>
       </c>
       <c r="F45" s="3">
-        <v>1600</v>
+        <v>900</v>
       </c>
       <c r="G45" s="3">
         <v>1600</v>
       </c>
       <c r="H45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>2500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>3600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1800</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>8900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>13300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>9100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>7700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>7400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>10500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>700</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
+      <c r="Z45" s="3">
+        <v>0</v>
       </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>83100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>85900</v>
+      </c>
+      <c r="F46" s="3">
         <v>82200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>79200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>80500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>80000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>83500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>86600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>99000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>102000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>92200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>88800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>100500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>103200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>106500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>110900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>110000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>161200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>152000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2700</v>
       </c>
-      <c r="X46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
+      <c r="Z46" s="3">
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3417,11 +3626,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3432,23 +3641,23 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>0</v>
       </c>
       <c r="U47" s="3">
-        <v>259200</v>
-      </c>
-      <c r="V47" s="3">
-        <v>259200</v>
+        <v>0</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>259200</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
+      <c r="X47" s="3">
+        <v>259200</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>259200</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
@@ -3456,68 +3665,74 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F48" s="3">
         <v>14200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>14800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>16200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>17500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>18400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>19500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>20100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>20300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>22000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>22900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>21600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>21900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>22600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>19800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>21200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>12200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>12600</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,68 +3748,74 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>301100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>311800</v>
+      </c>
+      <c r="F49" s="3">
         <v>322400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>333000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>343900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>353900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>367600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>376900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>453200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>462600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>470600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>558300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>553100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>562200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>626900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>638000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>649500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>585400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>594800</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3831,14 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3914,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,85 +3997,97 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F52" s="3">
         <v>4600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>5900</v>
-      </c>
-      <c r="F52" s="3">
-        <v>4500</v>
-      </c>
-      <c r="G52" s="3">
-        <v>4500</v>
       </c>
       <c r="H52" s="3">
         <v>4500</v>
       </c>
       <c r="I52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="K52" s="3">
         <v>4700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>4400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1200</v>
       </c>
       <c r="N52" s="3">
         <v>1200</v>
       </c>
       <c r="O52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>900</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3">
         <v>300</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,85 +4163,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>396100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>410500</v>
+      </c>
+      <c r="F54" s="3">
         <v>423400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>432900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>445100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>455800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>473900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>487700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>576600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>587000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>586200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>671300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>676500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>688700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>757500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>769400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>781400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>759600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>760400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>260400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>261500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>261800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>300</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4281,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,376 +4312,402 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F57" s="3">
         <v>17500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>19100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>18600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>14800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>22700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>21400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>22500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>24000</v>
       </c>
       <c r="L57" s="3">
         <v>22500</v>
       </c>
       <c r="M57" s="3">
+        <v>24000</v>
+      </c>
+      <c r="N57" s="3">
+        <v>22500</v>
+      </c>
+      <c r="O57" s="3">
         <v>21600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>23300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>17800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>18200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>19300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>19900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>16000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>20500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F58" s="3">
         <v>3100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>6300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>7000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>5500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>5400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>3200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>3500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>3700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>29800</v>
+      </c>
+      <c r="F59" s="3">
         <v>24600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>25300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>22300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>25700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>21400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>21700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>24400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>26100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>10100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>9700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>8900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>25500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>23400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>25200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>21400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>28700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>33400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>4600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>200</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>79300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>72000</v>
+      </c>
+      <c r="F60" s="3">
         <v>69100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>71600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>65400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>66100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>64500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>62600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>72300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>72000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>62800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>54000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>55100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>48800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>47100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>47800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>44500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>48200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>57700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>5600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>3400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>300</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>440500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>440400</v>
+      </c>
+      <c r="F61" s="3">
         <v>444900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>444900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>446700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>446700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>447000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>447100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>447300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>447200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>422400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>422400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>422100</v>
-      </c>
-      <c r="O61" s="3">
-        <v>414000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>414800</v>
       </c>
       <c r="Q61" s="3">
         <v>414000</v>
       </c>
       <c r="R61" s="3">
+        <v>414800</v>
+      </c>
+      <c r="S61" s="3">
         <v>414000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
+        <v>414000</v>
+      </c>
+      <c r="U61" s="3">
         <v>399400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>378700</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4438,85 +4723,97 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>61000</v>
+      </c>
+      <c r="F62" s="3">
         <v>54200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>47900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>44600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>38500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>33400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>27700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>22200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>17100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>15700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>12400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>11400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>70400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>44100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>43800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>47800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>39900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>40100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>23800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>18400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>21100</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4889,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4972,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,85 +5055,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>587600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>574300</v>
+      </c>
+      <c r="F66" s="3">
         <v>569100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>566400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>560000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>555400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>551200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>544900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>554300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>550000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>515100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>508200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>511800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>508000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>506000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>505500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>506300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>487500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>476400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>29400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>21800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>22100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>300</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5173,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5252,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5335,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5083,8 +5418,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,85 +5501,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-652800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-624300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-605800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-593100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-576300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-561400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-535900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-516500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-432900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-415300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-381600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-286200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-266700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-248200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-173000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-159900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-148800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-138200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-126200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-13600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-4900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-4900</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
+      <c r="Z72" s="3">
+        <v>0</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5667,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5750,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,85 +5833,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-191500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-163800</v>
+      </c>
+      <c r="F76" s="3">
         <v>-145700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-133500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-114900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-99600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-77200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-57200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>22300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>37000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>71100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>163000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>164700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>180700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>251500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>263900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>275100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>272100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>284000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>231000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>239700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>239800</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
+      <c r="Z76" s="3">
+        <v>0</v>
       </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5999,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-12700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-16900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-14900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-25400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-19400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-83600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-17600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-33700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-95400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-19500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-18500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-69600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-10800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-11600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-12000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-8300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-22900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-4900</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
+      <c r="Z81" s="3">
+        <v>0</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,65 +6205,67 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F83" s="3">
         <v>14200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>14400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>13600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>17600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>14500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>14000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>14700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>16100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>13700</v>
-      </c>
-      <c r="M83" s="3">
-        <v>13800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>13200</v>
       </c>
       <c r="O83" s="3">
         <v>13800</v>
       </c>
       <c r="P83" s="3">
-        <v>13700</v>
+        <v>13200</v>
       </c>
       <c r="Q83" s="3">
         <v>13800</v>
       </c>
       <c r="R83" s="3">
+        <v>13700</v>
+      </c>
+      <c r="S83" s="3">
+        <v>13800</v>
+      </c>
+      <c r="T83" s="3">
         <v>13200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>12500</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5881,14 +6278,20 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6367,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6450,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6533,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6616,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,85 +6699,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F89" s="3">
         <v>1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2900</v>
       </c>
-      <c r="G89" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J89" s="3">
         <v>1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>4000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-10900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>3200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-4200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>9800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>14700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-4000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-5300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-8200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-800</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
+      <c r="Z89" s="3">
+        <v>0</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,8 +6817,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6387,58 +6828,58 @@
         <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-4600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-3800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-3400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-3600</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -6449,14 +6890,20 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6979,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,65 +7062,71 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-2300</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J94" s="3">
         <v>-3400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-4700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-4600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-5400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-5400</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-4600</v>
       </c>
       <c r="P94" s="3">
         <v>-4800</v>
       </c>
       <c r="Q94" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="R94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="S94" s="3">
         <v>-4700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-48500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-3600</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6680,14 +7139,20 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +7180,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6753,11 +7220,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6792,8 +7259,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7342,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7425,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,8 +7508,14 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7032,56 +7523,56 @@
         <v>-500</v>
       </c>
       <c r="E100" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="F100" s="3">
         <v>-500</v>
       </c>
       <c r="G100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I100" s="3">
         <v>-400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>22700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>22300</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7094,14 +7585,20 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7109,55 +7606,55 @@
         <v>200</v>
       </c>
       <c r="E101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F101" s="3">
+        <v>200</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G101" s="3">
-        <v>300</v>
       </c>
       <c r="H101" s="3">
         <v>-200</v>
       </c>
       <c r="I101" s="3">
+        <v>300</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>1600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
@@ -7171,87 +7668,99 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-3700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>7400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-7500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-4000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-8300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>2500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>8500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-54100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>13300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>63600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1900</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
+      <c r="Z102" s="3">
+        <v>0</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
